--- a/outputs/ranker/baseline/ranker_training_report.xlsx
+++ b/outputs/ranker/baseline/ranker_training_report.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="79">
   <si>
     <t>model_type</t>
   </si>
@@ -28,19 +28,28 @@
     <t>feature_count</t>
   </si>
   <si>
+    <t>cv_folds</t>
+  </si>
+  <si>
     <t>mae_in_sample</t>
   </si>
   <si>
     <t>r2_in_sample</t>
   </si>
   <si>
+    <t>mae_cv</t>
+  </si>
+  <si>
+    <t>r2_cv</t>
+  </si>
+  <si>
     <t>note</t>
   </si>
   <si>
     <t>gradient_boosting</t>
   </si>
   <si>
-    <t>MVP용 소규모 데이터의 in-sample 결과입니다. 생산 모델 성능으로 과장하지 않고 암묵지 학습 실증 개념으로 해석해야 합니다.</t>
+    <t>MVP용 소규모 데이터 결과입니다. 생산 모델 성능으로 과장하지 않고 암묵지 학습 실증 개념으로 해석해야 합니다. 5-fold 교차검증 out-of-sample 지표(mae_cv/r2_cv)를 함께 산출했습니다. 일반화 성능은 in-sample이 아닌 CV 기준으로 해석해야 합니다.</t>
   </si>
   <si>
     <t>scenario_name</t>
@@ -226,19 +235,19 @@
     <t>OPTIMAL</t>
   </si>
   <si>
-    <t>/mnt/data/work_v05/G-LIFT_v.0.4.0_optimizer_stabilized_ranker_spec/outputs/candidates/baseline/candidate_01_min_unserved.xlsx</t>
-  </si>
-  <si>
-    <t>/mnt/data/work_v05/G-LIFT_v.0.4.0_optimizer_stabilized_ranker_spec/outputs/candidates/baseline/candidate_02_fairness.xlsx</t>
-  </si>
-  <si>
-    <t>/mnt/data/work_v05/G-LIFT_v.0.4.0_optimizer_stabilized_ranker_spec/outputs/candidates/baseline/candidate_03_vehicle_preservation.xlsx</t>
-  </si>
-  <si>
-    <t>/mnt/data/work_v05/G-LIFT_v.0.4.0_optimizer_stabilized_ranker_spec/outputs/candidates/baseline/candidate_04_fatigue.xlsx</t>
-  </si>
-  <si>
-    <t>/mnt/data/work_v05/G-LIFT_v.0.4.0_optimizer_stabilized_ranker_spec/outputs/candidates/baseline/candidate_05_expert_style.xlsx</t>
+    <t>/home/hk416an/dev/Bus/outputs/candidates/baseline/candidate_01_min_unserved.xlsx</t>
+  </si>
+  <si>
+    <t>/home/hk416an/dev/Bus/outputs/candidates/baseline/candidate_02_fairness.xlsx</t>
+  </si>
+  <si>
+    <t>/home/hk416an/dev/Bus/outputs/candidates/baseline/candidate_03_vehicle_preservation.xlsx</t>
+  </si>
+  <si>
+    <t>/home/hk416an/dev/Bus/outputs/candidates/baseline/candidate_04_fatigue.xlsx</t>
+  </si>
+  <si>
+    <t>/home/hk416an/dev/Bus/outputs/candidates/baseline/candidate_05_expert_style.xlsx</t>
   </si>
   <si>
     <t>feature</t>
@@ -602,10 +611,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -624,10 +633,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -636,13 +654,22 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>0.03813040597024724</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>0.9999935985735532</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
+        <v>0.1253918292906548</v>
+      </c>
+      <c r="F2">
+        <v>0.9999404337602056</v>
+      </c>
+      <c r="G2">
+        <v>12.66241048217999</v>
+      </c>
+      <c r="H2">
+        <v>-0.4119562226948621</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -657,50 +684,50 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2">
-        <v>0.9980205641095037</v>
+        <v>0.9974474371572508</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -709,30 +736,30 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>0.9935368070037682</v>
+        <v>0.9974474371572508</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -747,150 +774,150 @@
   <sheetData>
     <row r="1" spans="1:44">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="AR1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:44">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E2">
         <v>34</v>
@@ -926,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.444436223734833</v>
+        <v>0.6274950801236998</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -959,16 +986,16 @@
         <v>540</v>
       </c>
       <c r="AA2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB2">
-        <v>17.647</v>
+        <v>23.529</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD2">
-        <v>3.571</v>
+        <v>7.143</v>
       </c>
       <c r="AE2">
         <v>5</v>
@@ -983,48 +1010,48 @@
         <v>100</v>
       </c>
       <c r="AI2">
-        <v>43.736</v>
+        <v>46.688</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.04347296787309935</v>
+        <v>0.08695810963807019</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AN2">
-        <v>76.05423999999999</v>
+        <v>76.50287</v>
       </c>
       <c r="AO2">
-        <v>43.7934912312782</v>
+        <v>46.66154313427446</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.2519774753419622</v>
+        <v>0.2947616366154081</v>
       </c>
       <c r="AR2">
-        <v>0.2232841840550933</v>
+        <v>0.2382725610905625</v>
       </c>
     </row>
     <row r="3" spans="1:44">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E3">
         <v>34</v>
@@ -1054,13 +1081,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>0.4687614176105219</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.2104912696063923</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1078,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="V3">
-        <v>0.5714285714285714</v>
+        <v>0.4</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -1120,7 +1147,7 @@
         <v>46.824</v>
       </c>
       <c r="AJ3">
-        <v>0.1071484948939322</v>
+        <v>0.03847210053484328</v>
       </c>
       <c r="AK3">
         <v>0.04347296787309935</v>
@@ -1129,36 +1156,36 @@
         <v>0</v>
       </c>
       <c r="AM3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AN3">
-        <v>75.71343999999999</v>
+        <v>75.23186</v>
       </c>
       <c r="AO3">
-        <v>46.85639184001016</v>
+        <v>46.94281661630287</v>
       </c>
       <c r="AP3">
-        <v>0.06371476911649405</v>
+        <v>0.002988091576218212</v>
       </c>
       <c r="AQ3">
-        <v>0.1646994769048391</v>
+        <v>0.05754202607881254</v>
       </c>
       <c r="AR3">
-        <v>0.1601682753100317</v>
+        <v>0.09809725342039713</v>
       </c>
     </row>
     <row r="4" spans="1:44">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E4">
         <v>34</v>
@@ -1188,13 +1215,13 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>0.4666987642432997</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>0.2963171211695253</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -1212,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="V4">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W4">
         <v>0</v>
@@ -1233,10 +1260,10 @@
         <v>29.412</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>3.571</v>
       </c>
       <c r="AE4">
         <v>5</v>
@@ -1251,48 +1278,48 @@
         <v>100</v>
       </c>
       <c r="AI4">
-        <v>46.961</v>
+        <v>47.854</v>
       </c>
       <c r="AJ4">
-        <v>0.1428606122424198</v>
+        <v>0.07693112421702343</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>0.04347296787309935</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AN4">
-        <v>75.14403999999999</v>
+        <v>75.72197</v>
       </c>
       <c r="AO4">
-        <v>46.96644294363724</v>
+        <v>48.04866295692377</v>
       </c>
       <c r="AP4">
-        <v>0.06654149300540588</v>
+        <v>0.02561849101375394</v>
       </c>
       <c r="AQ4">
-        <v>0.06889635435837743</v>
+        <v>0.1724980856091174</v>
       </c>
       <c r="AR4">
-        <v>0.101143030612121</v>
+        <v>0.1587652918682699</v>
       </c>
     </row>
     <row r="5" spans="1:44">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E5">
         <v>34</v>
@@ -1322,13 +1349,13 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>0.4687614176105219</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.444436223734833</v>
+        <v>0.2963171211695253</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -1361,10 +1388,10 @@
         <v>540</v>
       </c>
       <c r="AA5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB5">
-        <v>38.235</v>
+        <v>35.294</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1385,10 +1412,10 @@
         <v>100</v>
       </c>
       <c r="AI5">
-        <v>50.049</v>
+        <v>49.02</v>
       </c>
       <c r="AJ5">
-        <v>0.2499969642878827</v>
+        <v>0.1538491715813838</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -1397,36 +1424,36 @@
         <v>0</v>
       </c>
       <c r="AM5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AN5">
-        <v>76.09411999999999</v>
+        <v>75.5758</v>
       </c>
       <c r="AO5">
-        <v>50.03060684747887</v>
+        <v>48.85282295672324</v>
       </c>
       <c r="AP5">
-        <v>0.1302562621218999</v>
+        <v>0.05123698202750804</v>
       </c>
       <c r="AQ5">
-        <v>0.2212852953210594</v>
+        <v>0.1179641005309339</v>
       </c>
       <c r="AR5">
-        <v>0.1757989114607794</v>
+        <v>0.1184346570609359</v>
       </c>
     </row>
     <row r="6" spans="1:44">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E6">
         <v>34</v>
@@ -1480,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="V6">
-        <v>0.2571428571428571</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1531,22 +1558,22 @@
         <v>0</v>
       </c>
       <c r="AM6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AN6">
-        <v>82.57122999999999</v>
+        <v>83.85393999999999</v>
       </c>
       <c r="AO6">
-        <v>92.12506713759549</v>
+        <v>92.08215433577567</v>
       </c>
       <c r="AP6">
         <v>1</v>
       </c>
       <c r="AQ6">
-        <v>0.6681571428571429</v>
+        <v>0.6684142857142857</v>
       </c>
       <c r="AR6">
-        <v>0.2625714285714286</v>
+        <v>0.2631428571428572</v>
       </c>
     </row>
   </sheetData>
@@ -1561,47 +1588,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B2">
-        <v>0.5242899508664018</v>
+        <v>0.5295280981156625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B3">
-        <v>0.4636877694261007</v>
+        <v>0.4684261329512984</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B4">
-        <v>0.008807235762819519</v>
+        <v>0.001717338277104945</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B5">
-        <v>0.003215043944677783</v>
+        <v>0.0003284306559341352</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1609,7 +1636,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1617,7 +1644,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1625,7 +1652,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1633,7 +1660,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1641,7 +1668,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1649,7 +1676,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1657,7 +1684,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1665,7 +1692,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1673,7 +1700,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1681,7 +1708,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1689,7 +1716,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B17">
         <v>0</v>
